--- a/public/training/library/training-samples/SBD-Training-SCTM-SP800-53r5.xlsx
+++ b/public/training/library/training-samples/SBD-Training-SCTM-SP800-53r5.xlsx
@@ -52,7 +52,7 @@
     <t xml:space="preserve">SECURE BY DESIGN TRAINING SAMPLE - NOT AN OFFICIAL FORM. For instruction and practice with fictional data only.</t>
   </si>
   <si>
-    <t xml:space="preserve">[CLASSIFICATION: when filled in, mark this document as your security classification guide and PSO direct]</t>
+    <t/>
   </si>
   <si>
     <t xml:space="preserve">Security Control Traceability Matrix (SCTM) - training sample</t>
@@ -6807,10 +6807,8 @@
       </c>
       <c r="B1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="4" customHeight="1">
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6982,10 +6980,8 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="4" customHeight="1">
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -42459,10 +42455,8 @@
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="4" customHeight="1">
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
